--- a/forms/trg/Formulir_TRG_powersystems.xlsx
+++ b/forms/trg/Formulir_TRG_powersystems.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B29)</f>
+        <f>COUNTA(Anggota!B5:B30)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F29)</f>
+        <f>COUNTA(Anggota!F5:F30)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Sri Mawar Said, M.T</t>
+          <t>Prof. Dr.Eng. Ir. Syafaruddin, S.T., M.Eng., IPU</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,18 +928,22 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Power Generation and Load Management</t>
+          <t>Renewable Energy and Artificial Intelligence</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-9915-7694</t>
+        </is>
+      </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57190658413</t>
+          <t>23502333600</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -954,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ir. Yusri Syam Akil, S.T., M.T., Ph.D</t>
+          <t>Prof. Dr. Ir. Sri Mawar Said, M.T</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -969,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Energy Management Systems</t>
+          <t>Power Generation and Load Management</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -980,7 +984,7 @@
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>16318555700</t>
+          <t>57190658413</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -995,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ian Adran Bustanuddin, S.T., M.T</t>
+          <t>Prof. Ir. Yusri Syam Akil, S.T., M.T., Ph.D</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1010,7 +1014,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Hybrid Energy Systems</t>
+          <t>Energy Management Systems</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1019,7 +1023,11 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>16318555700</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1032,39 +1040,31 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Donald S. Zinger</t>
+          <t>Ian Adran Bustanuddin, S.T., M.T</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Northern Illinois University (NIU), USA</t>
+          <t>Department of Electrical Engineering</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Electrical Engineering Technology</t>
+          <t>Hybrid Energy Systems</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0009-0000-1453-5274</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>7003310346</t>
-        </is>
-      </c>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1077,22 +1077,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Anuar Mohamad</t>
+          <t>Prof. Donald S. Zinger</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Universiti Teknologi Mara (UiTM), Malaysia</t>
+          <t>Northern Illinois University (NIU), USA</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Renewable Energy Management Systems</t>
+          <t>Electrical Engineering Technology</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1101,13 +1101,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5520-0438</t>
+          <t>0009-0000-1453-5274</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>58220982000</t>
+          <t>7003310346</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1122,22 +1122,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Yaser Qudaih</t>
+          <t>Dr. Anuar Mohamad</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Higher Colleges of Technology, United Arab Emirates (UAE)</t>
+          <t>Universiti Teknologi Mara (UiTM), Malaysia</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Energy and Environment Systems</t>
+          <t>Renewable Energy Management Systems</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1146,13 +1146,13 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7259-865X</t>
+          <t>0000-0001-5520-0438</t>
         </is>
       </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>24776887100</t>
+          <t>58220982000</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1167,31 +1167,39 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Moethia Faridha</t>
+          <t>Dr. Yaser Qudaih</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Department of Electrical Engineering</t>
+          <t>Higher Colleges of Technology, United Arab Emirates (UAE)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Load Shedding with Artificial Intelligence</t>
+          <t>Energy and Environment Systems</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-7259-865X</t>
+        </is>
+      </c>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>24776887100</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1204,12 +1212,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Saiful Karim</t>
+          <t>Moethia Faridha</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1219,7 +1227,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Energy Management of Electric Vehicle</t>
+          <t>Load Shedding with Artificial Intelligence</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1241,22 +1249,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Purwadi</t>
+          <t>Saiful Karim</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency (BRIN)</t>
+          <t>Department of Electrical Engineering</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Wind Tunnel with Machine Learning</t>
+          <t>Energy Management of Electric Vehicle</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1265,11 +1273,7 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>58260856900</t>
-        </is>
-      </c>
+      <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1282,22 +1286,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Putri Aisyah Kurnia</t>
+          <t>Purwadi</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Department of Electrical Engineering</t>
+          <t>National Research and Innovation Agency (BRIN)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Solar Cells Materials</t>
+          <t>Wind Tunnel with Machine Learning</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1308,7 +1312,7 @@
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>58870050500</t>
+          <t>58260856900</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1323,12 +1327,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Indah Nursusilowati</t>
+          <t>Putri Aisyah Kurnia</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1338,7 +1342,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Vertical Axis Wind Turbine</t>
+          <t>Solar Cells Materials</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1347,7 +1351,11 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>58870050500</t>
+        </is>
+      </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1360,12 +1368,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Khairus Shabri Achmad</t>
+          <t>Indah Nursusilowati</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1375,7 +1383,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Wind Power based PMSG Control</t>
+          <t>Vertical Axis Wind Turbine</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1397,12 +1405,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Nawir</t>
+          <t>Khairus Shabri Achmad</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1412,7 +1420,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Modelling of Energy Systems</t>
+          <t>Wind Power based PMSG Control</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1432,10 +1440,26 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Muhammad Nawir</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Modelling of Energy Systems</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Power system research group utilizes computational intelligence methods for solving wide-area problems including distributed generation planning, real-time simulation, renewable energy especially photovoltaic system includes MPP control, inverter configuration, partially shaded cases and fault-tolerant for household PV application and intelligent control application to power system includes artificial neural network, fuzzy logic control, genetic algorithm, evolutionary algorithm, particle swarm optimization and chaos theory.</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1443,7 +1467,11 @@
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1632,15 +1660,32 @@
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="12" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
